--- a/jogos_2025-04-28.xlsx
+++ b/jogos_2025-04-28.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="X5" t="n">
         <v>2</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1', '-1']</t>
+          <t>['45+9']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45775.45833333334</v>
@@ -1149,32 +1149,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Radnički Sr. Mitrovica</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Inđija</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD6" t="n">
         <v>1.75</v>
       </c>
-      <c r="M6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>2.38</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['-1', '-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45775.45833333334</v>
@@ -1278,32 +1278,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,65 +1314,65 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.65</v>
       </c>
       <c r="X7" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['-1', '-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1381,16 +1381,16 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45775.45833333334</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Voska Sport</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.92</v>
+        <v>2.34</v>
       </c>
       <c r="M8" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="O8" t="n">
-        <v>3.64</v>
+        <v>2.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="W8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Z8" t="n">
         <v>1.75</v>
       </c>
-      <c r="X8" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AA8" t="n">
-        <v>5.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['45+9']</t>
+          <t>['-1', '-1', '-1']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45775.45833333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Radnički Sr. Mitrovica</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Voska Sport</t>
+          <t>Inđija</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.34</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>2.79</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.44</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AA9" t="n">
-        <v>3.6</v>
+        <v>2.06</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45775.45833333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,65 +1701,65 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>3.35</v>
       </c>
       <c r="M10" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>5.1</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
-        <v>1.91</v>
+        <v>3.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['49', '85']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45775.47916666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,22 +1804,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,65 +1830,65 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.35</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['49', '85']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.73</v>
+        <v>4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45775.47916666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Levadiakos</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lamia</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="Z12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['29']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1.33</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45775.5</v>
@@ -2052,32 +2052,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="P13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['4', '78', '84']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.1</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45775.5</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="T15" t="n">
-        <v>3.04</v>
+        <v>3.4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['22']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['48']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45775.5</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kallithea</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.73</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O16" t="n">
         <v>3.5</v>
       </c>
-      <c r="N16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.29</v>
-      </c>
       <c r="P16" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.62</v>
+        <v>3.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['4', '78', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45775.5</v>
@@ -2568,35 +2568,35 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kallithea</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,49 +2604,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2655,21 +2655,21 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['42']</t>
-        </is>
-      </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
@@ -2677,10 +2677,10 @@
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45775.5</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N18" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
@@ -2757,10 +2757,10 @@
         <v>2.63</v>
       </c>
       <c r="T18" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2784,10 +2784,10 @@
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['48']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG18" t="n">
@@ -2806,10 +2806,10 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45775.5</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Levadiakos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Lamia</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="O19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="R19" t="n">
         <v>1.44</v>
@@ -2886,10 +2886,10 @@
         <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2913,10 +2913,10 @@
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2935,10 +2935,10 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.88</v>
+        <v>4.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45775.5</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mladost Lučani</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Mladost Novi Sad</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -3249,22 +3249,22 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="N22" t="n">
-        <v>2.85</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>2.64</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3307,12 +3307,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG22" t="n">
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45775.54166666666</v>
@@ -3342,33 +3342,33 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mladost Novi Sad</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="M23" t="n">
-        <v>2.73</v>
+        <v>4.24</v>
       </c>
       <c r="N23" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="Q23" t="n">
         <v>5</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.64</v>
+        <v>1.53</v>
       </c>
       <c r="Z23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>['22', '76']</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>['90', '90+7']</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45775.54166666666</v>
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
         <v>3</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M24" t="n">
+      <c r="U24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA24" t="n">
         <v>3.8</v>
       </c>
-      <c r="N24" t="n">
-        <v>5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="AB24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>['61', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>2.25</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['22', '39', '45', '73', '88']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45775.54166666666</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Mladost Lučani</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
         <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="O26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="n">
         <v>1.67</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['61', '90+5']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45775.54166666666</v>
@@ -3858,32 +3858,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M27" t="n">
-        <v>4.24</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="P27" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.59</v>
+        <v>1.47</v>
       </c>
       <c r="V27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X27" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['22', '76']</t>
+          <t>['22', '39', '45', '73', '88']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>['90', '90+7']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AI27" t="n">
         <v>1.4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45775.54166666666</v>
@@ -4374,35 +4374,35 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
         <v>1</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.3</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="P31" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>2.5</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
-        <v>1.49</v>
+        <v>3.48</v>
       </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '90']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['26', '30', '61']</t>
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45775.58333333334</v>
@@ -4513,19 +4513,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="M32" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P32" t="n">
         <v>2.35</v>
       </c>
-      <c r="O32" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Q32" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="T32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.35</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X32" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC32" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC32" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['53', '57', '75']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['15', '59']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45775.58333333334</v>
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,34 +4797,34 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="N34" t="n">
-        <v>1.7</v>
+        <v>2.04</v>
       </c>
       <c r="O34" t="n">
-        <v>4.68</v>
+        <v>3.65</v>
       </c>
       <c r="P34" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U34" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="V34" t="n">
         <v>1.03</v>
@@ -4836,41 +4836,41 @@
         <v>4.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['20', '36', '62', '67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ34" t="n">
         <v>1.62</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,22 +4900,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.25</v>
+        <v>3.38</v>
       </c>
       <c r="M35" t="n">
-        <v>3.53</v>
+        <v>2.46</v>
       </c>
       <c r="N35" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="O35" t="n">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="P35" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="S35" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="T35" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="U35" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="V35" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="W35" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="X35" t="n">
-        <v>3.9</v>
+        <v>2.13</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.87</v>
+        <v>2.88</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.03</v>
+        <v>1.32</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.84</v>
+        <v>5.7</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['27', '66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>['55', '65']</t>
+          <t>['58', '61']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.57</v>
+        <v>2.63</v>
       </c>
       <c r="AJ35" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45775.58333333334</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
         <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -5184,83 +5184,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3.38</v>
+        <v>2.25</v>
       </c>
       <c r="M37" t="n">
-        <v>2.46</v>
+        <v>3.53</v>
       </c>
       <c r="N37" t="n">
-        <v>2.74</v>
+        <v>2.95</v>
       </c>
       <c r="O37" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="P37" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="S37" t="n">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="T37" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="U37" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="V37" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="W37" t="n">
-        <v>1.65</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
-        <v>2.13</v>
+        <v>3.9</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.88</v>
+        <v>1.87</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.32</v>
+        <v>2.03</v>
       </c>
       <c r="AA37" t="n">
-        <v>5.7</v>
+        <v>2.84</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '66']</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>['58', '61']</t>
+          <t>['55', '65']</t>
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="AK37" s="3" t="n">
         <v>45775.58333333334</v>
@@ -5277,119 +5277,119 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>2</v>
       </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.71</v>
+        <v>4.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>4.5</v>
+        <v>1.7</v>
       </c>
       <c r="O38" t="n">
-        <v>2.3</v>
+        <v>4.68</v>
       </c>
       <c r="P38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z38" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q38" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z38" t="n">
+      <c r="AA38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2</v>
-      </c>
       <c r="AD38" t="n">
-        <v>1.75</v>
+        <v>2.15</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>['35', '45+1', '54']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '36', '62', '67']</t>
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45775.58333333334</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,22 +5416,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.53</v>
+        <v>2.24</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
       <c r="N39" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
-        <v>2.03</v>
+        <v>2.88</v>
       </c>
       <c r="P39" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="R39" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="T39" t="n">
-        <v>2.53</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="V39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.09</v>
+        <v>1.7</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD39" t="n">
         <v>1.83</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '42', '64', '86']</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>['88']</t>
+          <t>['75']</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="AJ39" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45775.58333333334</v>
@@ -5535,26 +5535,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>2</v>
@@ -5571,83 +5571,83 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="M40" t="n">
-        <v>2.45</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>3.9</v>
+        <v>2.35</v>
       </c>
       <c r="O40" t="n">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P40" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="R40" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X40" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>['53', '57', '75']</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>['15', '59']</t>
+        </is>
+      </c>
+      <c r="AG40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ40" t="n">
         <v>1.73</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2</v>
-      </c>
-      <c r="T40" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="U40" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>['45+5', '70']</t>
-        </is>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45775.58333333334</v>
@@ -5664,35 +5664,35 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>2</v>
       </c>
-      <c r="H41" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3.41</v>
+        <v>1.71</v>
       </c>
       <c r="M41" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.03</v>
+        <v>4.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="P41" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.58</v>
+        <v>5.5</v>
       </c>
       <c r="R41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U41" t="n">
         <v>1.33</v>
       </c>
-      <c r="S41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.48</v>
-      </c>
       <c r="V41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD41" t="n">
         <v>1.75</v>
       </c>
-      <c r="Z41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>['53', '86']</t>
+          <t>['35', '45+1', '54']</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>['6', '58', '88']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45775.58333333334</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,87 +5803,87 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
@@ -5892,20 +5892,20 @@
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45775.58333333334</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5947,94 +5947,94 @@
         <v>3</v>
       </c>
       <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" t="n">
-        <v>2</v>
-      </c>
       <c r="K43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.57</v>
+        <v>3.41</v>
       </c>
       <c r="M43" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O43" t="n">
         <v>3.9</v>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2.08</v>
       </c>
       <c r="P43" t="n">
         <v>2.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="R43" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S43" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T43" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="U43" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="V43" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W43" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X43" t="n">
-        <v>3.48</v>
+        <v>3.8</v>
       </c>
       <c r="Y43" t="n">
         <v>1.75</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.35</v>
+        <v>2.71</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>['8', '90']</t>
+          <t>['53', '86']</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>['26', '30', '61']</t>
+          <t>['6', '58', '88']</t>
         </is>
       </c>
       <c r="AG43" t="n">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.25</v>
+        <v>1.16</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.44</v>
+        <v>2.4</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK43" s="3" t="n">
         <v>45775.58333333334</v>
@@ -6051,32 +6051,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -6087,70 +6087,70 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.89</v>
+        <v>2.45</v>
       </c>
       <c r="M44" t="n">
-        <v>3.79</v>
+        <v>2.45</v>
       </c>
       <c r="N44" t="n">
-        <v>1.82</v>
+        <v>3.9</v>
       </c>
       <c r="O44" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P44" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S44" t="n">
+        <v>2</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
         <v>2.63</v>
       </c>
-      <c r="R44" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U44" t="n">
+      <c r="AD44" t="n">
         <v>1.44</v>
       </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>['20', '84']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>['29', '71']</t>
+          <t>['45+5', '70']</t>
         </is>
       </c>
       <c r="AG44" t="n">
@@ -6160,10 +6160,10 @@
         <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45775.58333333334</v>
@@ -6180,32 +6180,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -6216,70 +6216,70 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.24</v>
+        <v>3.3</v>
       </c>
       <c r="M45" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="O45" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="P45" t="n">
         <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Y45" t="n">
         <v>2</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['25', '42', '64', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG45" t="n">
@@ -6289,10 +6289,10 @@
         <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45775.58333333334</v>
@@ -6309,29 +6309,29 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -6345,61 +6345,61 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.34</v>
+        <v>1.53</v>
       </c>
       <c r="M46" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="N46" t="n">
-        <v>2.04</v>
+        <v>5.5</v>
       </c>
       <c r="O46" t="n">
-        <v>3.65</v>
+        <v>2.03</v>
       </c>
       <c r="P46" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="R46" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T46" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
       <c r="U46" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="V46" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W46" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="X46" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y46" t="n">
         <v>1.65</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="AG46" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.17</v>
+        <v>2.5</v>
       </c>
       <c r="AI46" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45775.58333333334</v>
@@ -6954,32 +6954,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Santa Fe</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6990,70 +6990,70 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.88</v>
+        <v>5.25</v>
       </c>
       <c r="M51" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="N51" t="n">
-        <v>2.63</v>
+        <v>1.53</v>
       </c>
       <c r="O51" t="n">
+        <v>5</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R51" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S51" t="n">
         <v>3.75</v>
       </c>
-      <c r="P51" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R51" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S51" t="n">
-        <v>2.2</v>
-      </c>
       <c r="T51" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="U51" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
       </c>
       <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC51" t="n">
         <v>1.53</v>
       </c>
-      <c r="X51" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AD51" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>['43', '86']</t>
+          <t>['36', '42']</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['32', '54', '65']</t>
         </is>
       </c>
       <c r="AG51" t="n">
@@ -7063,10 +7063,10 @@
         <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="AJ51" t="n">
-        <v>1.91</v>
+        <v>1.36</v>
       </c>
       <c r="AK51" s="3" t="n">
         <v>45775.625</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,109 +7093,109 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kazincbarcika</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
       </c>
       <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="M52" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N52" t="n">
         <v>2</v>
       </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="M52" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N52" t="n">
-        <v>2.7</v>
-      </c>
       <c r="O52" t="n">
-        <v>3.2</v>
+        <v>4.75</v>
       </c>
       <c r="P52" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="R52" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S52" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="T52" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="U52" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="V52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AA52" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>['7', '40', '58', '83']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AK52" s="3" t="n">
         <v>45775.625</v>
@@ -7351,25 +7351,25 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -7377,70 +7377,70 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="M54" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N54" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S54" t="n">
         <v>3.5</v>
       </c>
-      <c r="N54" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P54" t="n">
+      <c r="T54" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD54" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q54" t="n">
-        <v>3</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S54" t="n">
-        <v>4</v>
-      </c>
-      <c r="T54" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>3</v>
-      </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47', '49', '59']</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>['29', '75']</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG54" t="n">
@@ -7450,10 +7450,10 @@
         <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="AJ54" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AK54" s="3" t="n">
         <v>45775.625</v>
@@ -7480,60 +7480,60 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>2</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O55" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q55" t="n">
         <v>3</v>
       </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="O55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P55" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>2.63</v>
-      </c>
       <c r="R55" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S55" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T55" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U55" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
@@ -7545,31 +7545,31 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.35</v>
+        <v>2.88</v>
       </c>
       <c r="AA55" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>['47', '49', '59']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['29', '75']</t>
         </is>
       </c>
       <c r="AG55" t="n">
@@ -7579,10 +7579,10 @@
         <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.25</v>
+        <v>1.73</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AK55" s="3" t="n">
         <v>45775.625</v>
@@ -7728,35 +7728,35 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Unión Santa Fe</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="n">
         <v>1</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -7764,70 +7764,70 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>3.77</v>
+        <v>2.88</v>
       </c>
       <c r="M57" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="N57" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="O57" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="R57" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S57" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T57" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U57" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y57" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z57" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD57" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>['85']</t>
+          <t>['43', '86']</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['33']</t>
         </is>
       </c>
       <c r="AG57" t="n">
@@ -7837,10 +7837,10 @@
         <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AK57" s="3" t="n">
         <v>45775.625</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,19 +7867,19 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Kazincbarcika</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
         <v>2</v>
@@ -7893,83 +7893,83 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>5.25</v>
+        <v>2.45</v>
       </c>
       <c r="M58" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="N58" t="n">
-        <v>1.53</v>
+        <v>2.7</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="P58" t="n">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="R58" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="S58" t="n">
-        <v>3.75</v>
+        <v>2.58</v>
       </c>
       <c r="T58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W58" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>['7', '40', '58', '83']</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ58" t="n">
         <v>2.1</v>
-      </c>
-      <c r="U58" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE58" t="inlineStr">
-        <is>
-          <t>['36', '42']</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>['32', '54', '65']</t>
-        </is>
-      </c>
-      <c r="AG58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>1.36</v>
       </c>
       <c r="AK58" s="3" t="n">
         <v>45775.625</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,25 +9028,25 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Estudiantes</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -9054,83 +9054,83 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="M67" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="N67" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O67" t="n">
         <v>4.2</v>
       </c>
-      <c r="O67" t="n">
-        <v>2.63</v>
-      </c>
       <c r="P67" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="R67" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S67" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="T67" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U67" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V67" t="n">
-        <v>3.59</v>
+        <v>1.13</v>
       </c>
       <c r="W67" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="X67" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Y67" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>['45']</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI67" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z67" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AK67" s="3" t="n">
         <v>45775.8125</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,23 +9286,23 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="G69" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
         <v>1</v>
       </c>
-      <c r="H69" t="n">
-        <v>2</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
@@ -9312,83 +9312,83 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="M69" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="N69" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O69" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S69" t="n">
         <v>2.3</v>
       </c>
-      <c r="O69" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P69" t="n">
+      <c r="T69" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X69" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC69" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q69" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S69" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T69" t="n">
-        <v>3</v>
-      </c>
-      <c r="U69" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V69" t="n">
-        <v>0</v>
-      </c>
-      <c r="W69" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X69" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Y69" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z69" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC69" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD69" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>['54']</t>
+          <t>['44', '90+2']</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>['72', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI69" t="n">
-        <v>2.2</v>
+        <v>1.73</v>
       </c>
       <c r="AJ69" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK69" s="3" t="n">
         <v>45775.8125</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,91 +9415,91 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Estudiantes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N70" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O70" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P70" t="n">
         <v>2</v>
       </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="M70" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="N70" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O70" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="P70" t="n">
-        <v>1.92</v>
-      </c>
       <c r="Q70" t="n">
-        <v>4.21</v>
+        <v>4.75</v>
       </c>
       <c r="R70" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S70" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T70" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V70" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X70" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Y70" t="n">
         <v>2.3</v>
       </c>
-      <c r="T70" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U70" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V70" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W70" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X70" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y70" t="n">
-        <v>2.55</v>
-      </c>
       <c r="Z70" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AA70" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>['44', '90+2']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -9508,16 +9508,16 @@
         </is>
       </c>
       <c r="AG70" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AJ70" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK70" s="3" t="n">
         <v>45775.8125</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,25 +9544,25 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -9570,83 +9570,83 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="M71" t="n">
-        <v>2.97</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="O71" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="P71" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R71" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="S71" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V71" t="n">
+        <v>0</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>['72', '87']</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
         <v>2.2</v>
       </c>
-      <c r="T71" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U71" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V71" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W71" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X71" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y71" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Z71" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA71" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC71" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD71" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF71" t="inlineStr">
-        <is>
-          <t>['45']</t>
-        </is>
-      </c>
-      <c r="AG71" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH71" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI71" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ71" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AK71" s="3" t="n">
         <v>45775.8125</v>
@@ -10060,19 +10060,19 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata</t>
+          <t>Independiente Rivadavia</t>
         </is>
       </c>
       <c r="G75" t="n">
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -10086,28 +10086,28 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="M75" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N75" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="O75" t="n">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="P75" t="n">
         <v>1.95</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="R75" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S75" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="T75" t="n">
         <v>3.75</v>
@@ -10119,16 +10119,16 @@
         <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X75" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10137,19 +10137,19 @@
         <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76', '81']</t>
         </is>
       </c>
       <c r="AG75" t="n">
@@ -10159,10 +10159,10 @@
         <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ75" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AK75" s="3" t="n">
         <v>45775.90625</v>
@@ -10189,19 +10189,19 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Independiente Rivadavia</t>
+          <t>Gimnasia La Plata</t>
         </is>
       </c>
       <c r="G76" t="n">
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -10215,28 +10215,28 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="M76" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N76" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="O76" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="P76" t="n">
         <v>1.95</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="R76" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S76" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="T76" t="n">
         <v>3.75</v>
@@ -10248,37 +10248,37 @@
         <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="X76" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC76" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y76" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AD76" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>['76', '81']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG76" t="n">
@@ -10288,10 +10288,10 @@
         <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AJ76" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AK76" s="3" t="n">
         <v>45775.90625</v>
